--- a/resources/tool_kii_health_service_provider_iphra_v2.xlsx
+++ b/resources/tool_kii_health_service_provider_iphra_v2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B01EF86B-C6AD-48D2-B858-1A2BFEB4ECE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02CCE0E5-883A-4859-BC3A-B735B854F1C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{27C29DD6-0256-4DF1-82F8-B613F9F4F125}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="535">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="547">
   <si>
     <t>type</t>
   </si>
@@ -1635,16 +1635,52 @@
     <t>admin4c</t>
   </si>
   <si>
-    <t>52701, 52702</t>
-  </si>
-  <si>
-    <t>52701, 53001</t>
-  </si>
-  <si>
-    <t>52702, 53002</t>
-  </si>
-  <si>
     <t>Any other closing remarks by the interviewer?</t>
+  </si>
+  <si>
+    <t>14225, 14227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14208, 14209, 14210, 14211, 14212, 14213, 14214, 14215, 14216, 14217, 14218, 14219, 14221, 14220, 13701, 13702, 13703, 14208, 14222, 14223, </t>
+  </si>
+  <si>
+    <t>14224, 14225, 14226, 14227</t>
+  </si>
+  <si>
+    <t>10503, 10609</t>
+  </si>
+  <si>
+    <t>enum_id</t>
+  </si>
+  <si>
+    <t>Team 1</t>
+  </si>
+  <si>
+    <t>Équipe 1</t>
+  </si>
+  <si>
+    <t>Team 2</t>
+  </si>
+  <si>
+    <t>Équipe 2</t>
+  </si>
+  <si>
+    <t>Team 3</t>
+  </si>
+  <si>
+    <t>Équipe 3</t>
+  </si>
+  <si>
+    <t>Team 4</t>
+  </si>
+  <si>
+    <t>Équipe 4</t>
+  </si>
+  <si>
+    <t>Team 5</t>
+  </si>
+  <si>
+    <t>Équipe 5</t>
   </si>
 </sst>
 </file>
@@ -1691,7 +1727,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1728,6 +1764,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1741,7 +1783,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1760,11 +1802,22 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="7">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2449,8 +2502,8 @@
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>51001</v>
+      <c r="A17" s="12">
+        <v>14201</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>36</v>
@@ -2469,8 +2522,8 @@
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>51001</v>
+      <c r="A18" s="12">
+        <v>14201</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>18</v>
@@ -2489,8 +2542,8 @@
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>51001</v>
+      <c r="A19" s="12">
+        <v>14201</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>61</v>
@@ -2509,8 +2562,8 @@
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>51001</v>
+      <c r="A20" s="12">
+        <v>14201</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>18</v>
@@ -2529,8 +2582,8 @@
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>51103</v>
+      <c r="A21" s="12">
+        <v>14204</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>20</v>
@@ -2549,8 +2602,8 @@
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>51103</v>
+      <c r="A22" s="12">
+        <v>14204</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>18</v>
@@ -2569,8 +2622,8 @@
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>51101</v>
+      <c r="A23" s="12">
+        <v>14202</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>38</v>
@@ -2592,8 +2645,8 @@
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>51101</v>
+      <c r="A24" s="12">
+        <v>14202</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>38</v>
@@ -2615,8 +2668,8 @@
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>51102</v>
+      <c r="A25" s="12">
+        <v>14203</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>38</v>
@@ -2635,8 +2688,8 @@
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>51102</v>
+      <c r="A26" s="12">
+        <v>14203</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>38</v>
@@ -2661,8 +2714,8 @@
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>52202</v>
+      <c r="A27" s="12">
+        <v>14203</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>38</v>
@@ -2684,8 +2737,8 @@
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>52202</v>
+      <c r="A28" s="12">
+        <v>14203</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>38</v>
@@ -2704,8 +2757,8 @@
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>52105</v>
+      <c r="A29" s="12">
+        <v>14405</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>110</v>
@@ -2724,8 +2777,8 @@
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>52105</v>
+      <c r="A30" s="12">
+        <v>14405</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>114</v>
@@ -2747,8 +2800,8 @@
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>52105</v>
+      <c r="A31" s="12">
+        <v>14405</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>18</v>
@@ -2767,8 +2820,8 @@
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>52105</v>
+      <c r="A32" s="12">
+        <v>14405</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>114</v>
@@ -2790,8 +2843,8 @@
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>52105</v>
+      <c r="A33" s="12">
+        <v>14405</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>18</v>
@@ -2810,8 +2863,8 @@
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>51201</v>
+      <c r="A34" s="12">
+        <v>14207</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>38</v>
@@ -2830,8 +2883,8 @@
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>51201</v>
+      <c r="A35" s="12">
+        <v>14207</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>38</v>
@@ -2850,8 +2903,8 @@
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>51201</v>
+      <c r="A36" s="12">
+        <v>14207</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>38</v>
@@ -2870,8 +2923,8 @@
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>51201</v>
+      <c r="A37" s="12">
+        <v>14207</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>38</v>
@@ -2890,8 +2943,8 @@
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>51201</v>
+      <c r="A38" s="12">
+        <v>14207</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>38</v>
@@ -2910,8 +2963,8 @@
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>51201</v>
+      <c r="A39" s="12">
+        <v>14207</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>38</v>
@@ -2930,8 +2983,8 @@
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>51201</v>
+      <c r="A40" s="12">
+        <v>14207</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>38</v>
@@ -2950,8 +3003,8 @@
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>51201</v>
+      <c r="A41" s="12">
+        <v>14207</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>38</v>
@@ -2970,8 +3023,8 @@
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>51201</v>
+      <c r="A42" s="12">
+        <v>14207</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>38</v>
@@ -2990,8 +3043,8 @@
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>51201</v>
+      <c r="A43" s="12">
+        <v>14207</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>38</v>
@@ -3010,8 +3063,8 @@
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>51201</v>
+      <c r="A44" s="12">
+        <v>14207</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>38</v>
@@ -3030,8 +3083,8 @@
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45">
-        <v>51201</v>
+      <c r="A45" s="12">
+        <v>14207</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>38</v>
@@ -3050,8 +3103,8 @@
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <v>51201</v>
+      <c r="A46" s="12">
+        <v>14207</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>38</v>
@@ -3070,8 +3123,8 @@
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47">
-        <v>51201</v>
+      <c r="A47" s="12">
+        <v>14207</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>38</v>
@@ -3090,8 +3143,8 @@
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48">
-        <v>51201</v>
+      <c r="A48" s="12">
+        <v>14207</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>38</v>
@@ -3110,8 +3163,8 @@
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <v>51201</v>
+      <c r="A49" s="12">
+        <v>14207</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>38</v>
@@ -3130,8 +3183,8 @@
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>51201</v>
+      <c r="A50" s="12">
+        <v>14207</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>38</v>
@@ -3150,8 +3203,8 @@
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>51201</v>
+      <c r="A51" s="12">
+        <v>14207</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>38</v>
@@ -3170,8 +3223,8 @@
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>51201</v>
+      <c r="A52" s="12">
+        <v>14207</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>38</v>
@@ -3190,8 +3243,8 @@
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53">
-        <v>51201</v>
+      <c r="A53" s="12">
+        <v>14207</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>38</v>
@@ -3210,8 +3263,8 @@
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <v>51201</v>
+      <c r="A54" s="12">
+        <v>14207</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>20</v>
@@ -3230,8 +3283,8 @@
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55">
-        <v>51201</v>
+      <c r="A55" s="12">
+        <v>14207</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>18</v>
@@ -3250,8 +3303,8 @@
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56">
-        <v>51201</v>
+      <c r="A56" s="12">
+        <v>14207</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>38</v>
@@ -3273,8 +3326,8 @@
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57">
-        <v>51201</v>
+      <c r="A57" s="12">
+        <v>14207</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>38</v>
@@ -3296,8 +3349,8 @@
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58">
-        <v>51301</v>
+      <c r="A58" t="s">
+        <v>533</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>155</v>
@@ -3310,8 +3363,8 @@
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59">
-        <v>51301</v>
+      <c r="A59" s="12">
+        <v>14208</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>38</v>
@@ -3330,8 +3383,8 @@
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60">
-        <v>51301</v>
+      <c r="A60" s="12">
+        <v>14208</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>38</v>
@@ -3350,8 +3403,8 @@
       </c>
     </row>
     <row r="61" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A61">
-        <v>51401</v>
+      <c r="A61" s="12">
+        <v>14209</v>
       </c>
       <c r="B61" s="8" t="s">
         <v>20</v>
@@ -3367,8 +3420,8 @@
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62">
-        <v>51401</v>
+      <c r="A62" s="12">
+        <v>14209</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>38</v>
@@ -3387,8 +3440,8 @@
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63">
-        <v>51401</v>
+      <c r="A63" s="12">
+        <v>14209</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>20</v>
@@ -3404,8 +3457,8 @@
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64">
-        <v>51401</v>
+      <c r="A64" s="12">
+        <v>14209</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>38</v>
@@ -3424,8 +3477,8 @@
       </c>
     </row>
     <row r="65" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A65">
-        <v>51501</v>
+      <c r="A65" s="12">
+        <v>14210</v>
       </c>
       <c r="B65" s="8" t="s">
         <v>20</v>
@@ -3441,8 +3494,8 @@
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66">
-        <v>51501</v>
+      <c r="A66" s="12">
+        <v>14210</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>38</v>
@@ -3461,8 +3514,8 @@
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A67">
-        <v>51501</v>
+      <c r="A67" s="12">
+        <v>14210</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>20</v>
@@ -3478,8 +3531,8 @@
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68">
-        <v>51501</v>
+      <c r="A68" s="12">
+        <v>14210</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>38</v>
@@ -3498,8 +3551,8 @@
       </c>
     </row>
     <row r="69" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A69">
-        <v>51601</v>
+      <c r="A69" s="12">
+        <v>14211</v>
       </c>
       <c r="B69" s="8" t="s">
         <v>20</v>
@@ -3515,8 +3568,8 @@
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70">
-        <v>51601</v>
+      <c r="A70" s="12">
+        <v>14211</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>38</v>
@@ -3535,8 +3588,8 @@
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71">
-        <v>51601</v>
+      <c r="A71" s="12">
+        <v>14211</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>20</v>
@@ -3552,8 +3605,8 @@
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72">
-        <v>51601</v>
+      <c r="A72" s="12">
+        <v>14211</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>38</v>
@@ -3572,8 +3625,8 @@
       </c>
     </row>
     <row r="73" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A73">
-        <v>51701</v>
+      <c r="A73" s="12">
+        <v>14212</v>
       </c>
       <c r="B73" s="8" t="s">
         <v>20</v>
@@ -3589,8 +3642,8 @@
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74">
-        <v>51701</v>
+      <c r="A74" s="12">
+        <v>14212</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>38</v>
@@ -3609,8 +3662,8 @@
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75">
-        <v>51701</v>
+      <c r="A75" s="12">
+        <v>14212</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>20</v>
@@ -3626,8 +3679,8 @@
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76">
-        <v>51701</v>
+      <c r="A76" s="12">
+        <v>14212</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>38</v>
@@ -3646,8 +3699,8 @@
       </c>
     </row>
     <row r="77" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A77">
-        <v>51801</v>
+      <c r="A77" s="12">
+        <v>14213</v>
       </c>
       <c r="B77" s="8" t="s">
         <v>20</v>
@@ -3663,8 +3716,8 @@
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78">
-        <v>51801</v>
+      <c r="A78" s="12">
+        <v>14213</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>38</v>
@@ -3683,8 +3736,8 @@
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79">
-        <v>51801</v>
+      <c r="A79" s="12">
+        <v>14213</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>20</v>
@@ -3700,8 +3753,8 @@
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80">
-        <v>51801</v>
+      <c r="A80" s="12">
+        <v>14213</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>38</v>
@@ -3720,8 +3773,8 @@
       </c>
     </row>
     <row r="81" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A81">
-        <v>51901</v>
+      <c r="A81" s="12">
+        <v>14214</v>
       </c>
       <c r="B81" s="8" t="s">
         <v>20</v>
@@ -3737,8 +3790,8 @@
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82">
-        <v>51901</v>
+      <c r="A82" s="12">
+        <v>14214</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>38</v>
@@ -3757,8 +3810,8 @@
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83">
-        <v>51901</v>
+      <c r="A83" s="12">
+        <v>14214</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>20</v>
@@ -3774,8 +3827,8 @@
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84">
-        <v>51901</v>
+      <c r="A84" s="12">
+        <v>14214</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>38</v>
@@ -3794,8 +3847,8 @@
       </c>
     </row>
     <row r="85" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A85">
-        <v>52001</v>
+      <c r="A85" s="12">
+        <v>14215</v>
       </c>
       <c r="B85" s="8" t="s">
         <v>20</v>
@@ -3811,8 +3864,8 @@
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86">
-        <v>52001</v>
+      <c r="A86" s="12">
+        <v>14215</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>38</v>
@@ -3831,8 +3884,8 @@
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87">
-        <v>52001</v>
+      <c r="A87" s="12">
+        <v>14215</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>20</v>
@@ -3848,8 +3901,8 @@
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88">
-        <v>52001</v>
+      <c r="A88" s="12">
+        <v>14215</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>38</v>
@@ -3868,8 +3921,8 @@
       </c>
     </row>
     <row r="89" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A89">
-        <v>52101</v>
+      <c r="A89" s="12">
+        <v>14216</v>
       </c>
       <c r="B89" s="8" t="s">
         <v>20</v>
@@ -3885,8 +3938,8 @@
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90">
-        <v>52101</v>
+      <c r="A90" s="12">
+        <v>14216</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>38</v>
@@ -3905,8 +3958,8 @@
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91">
-        <v>52101</v>
+      <c r="A91" s="12">
+        <v>14216</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>20</v>
@@ -3922,8 +3975,8 @@
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92">
-        <v>52101</v>
+      <c r="A92" s="12">
+        <v>14216</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>38</v>
@@ -3942,8 +3995,8 @@
       </c>
     </row>
     <row r="93" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A93">
-        <v>52201</v>
+      <c r="A93" s="12">
+        <v>14217</v>
       </c>
       <c r="B93" s="8" t="s">
         <v>20</v>
@@ -3959,8 +4012,8 @@
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94">
-        <v>52201</v>
+      <c r="A94" s="12">
+        <v>14217</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>38</v>
@@ -3979,8 +4032,8 @@
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95">
-        <v>52201</v>
+      <c r="A95" s="12">
+        <v>14217</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>20</v>
@@ -3996,8 +4049,8 @@
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96">
-        <v>52201</v>
+      <c r="A96" s="12">
+        <v>14217</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>38</v>
@@ -4016,8 +4069,8 @@
       </c>
     </row>
     <row r="97" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A97">
-        <v>52301</v>
+      <c r="A97" s="12">
+        <v>14218</v>
       </c>
       <c r="B97" s="8" t="s">
         <v>20</v>
@@ -4033,8 +4086,8 @@
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98">
-        <v>52301</v>
+      <c r="A98" s="12">
+        <v>14218</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>38</v>
@@ -4053,8 +4106,8 @@
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99">
-        <v>52301</v>
+      <c r="A99" s="12">
+        <v>14218</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>20</v>
@@ -4070,8 +4123,8 @@
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100">
-        <v>52301</v>
+      <c r="A100" s="12">
+        <v>14218</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>38</v>
@@ -4090,8 +4143,8 @@
       </c>
     </row>
     <row r="101" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A101">
-        <v>52401</v>
+      <c r="A101" s="12">
+        <v>14219</v>
       </c>
       <c r="B101" s="8" t="s">
         <v>20</v>
@@ -4107,8 +4160,8 @@
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102">
-        <v>52401</v>
+      <c r="A102" s="12">
+        <v>14219</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>38</v>
@@ -4127,8 +4180,8 @@
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103">
-        <v>52401</v>
+      <c r="A103" s="12">
+        <v>14219</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>20</v>
@@ -4144,8 +4197,8 @@
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104">
-        <v>52401</v>
+      <c r="A104" s="12">
+        <v>14219</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>38</v>
@@ -4164,8 +4217,8 @@
       </c>
     </row>
     <row r="105" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A105">
-        <v>51301</v>
+      <c r="A105" s="12">
+        <v>14221</v>
       </c>
       <c r="B105" s="8" t="s">
         <v>20</v>
@@ -4181,8 +4234,8 @@
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106">
-        <v>51301</v>
+      <c r="A106" s="12">
+        <v>14221</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>38</v>
@@ -4201,8 +4254,8 @@
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107">
-        <v>51301</v>
+      <c r="A107" s="12">
+        <v>14221</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>20</v>
@@ -4218,8 +4271,8 @@
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108">
-        <v>51301</v>
+      <c r="A108" s="12">
+        <v>14221</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>38</v>
@@ -4238,8 +4291,8 @@
       </c>
     </row>
     <row r="109" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A109">
-        <v>52501</v>
+      <c r="A109" s="12">
+        <v>14220</v>
       </c>
       <c r="B109" s="8" t="s">
         <v>20</v>
@@ -4255,8 +4308,8 @@
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A110">
-        <v>52501</v>
+      <c r="A110" s="12">
+        <v>14220</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>38</v>
@@ -4275,8 +4328,8 @@
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A111">
-        <v>52501</v>
+      <c r="A111" s="12">
+        <v>14220</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>20</v>
@@ -4292,8 +4345,8 @@
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A112">
-        <v>52501</v>
+      <c r="A112" s="12">
+        <v>14220</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>38</v>
@@ -4312,8 +4365,8 @@
       </c>
     </row>
     <row r="113" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A113">
-        <v>52501</v>
+      <c r="A113" s="12">
+        <v>14220</v>
       </c>
       <c r="B113" s="8" t="s">
         <v>20</v>
@@ -4329,8 +4382,8 @@
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A114">
-        <v>52501</v>
+      <c r="A114" s="12">
+        <v>14220</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>38</v>
@@ -4349,8 +4402,8 @@
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A115">
-        <v>52501</v>
+      <c r="A115" s="12">
+        <v>14220</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>20</v>
@@ -4366,8 +4419,8 @@
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A116">
-        <v>52501</v>
+      <c r="A116" s="12">
+        <v>14220</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>38</v>
@@ -4386,8 +4439,8 @@
       </c>
     </row>
     <row r="117" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A117">
-        <v>46001</v>
+      <c r="A117" s="12">
+        <v>13701</v>
       </c>
       <c r="B117" s="8" t="s">
         <v>20</v>
@@ -4403,8 +4456,8 @@
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A118">
-        <v>46001</v>
+      <c r="A118" s="12">
+        <v>13701</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>38</v>
@@ -4423,8 +4476,8 @@
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A119">
-        <v>46001</v>
+      <c r="A119" s="12">
+        <v>13701</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>20</v>
@@ -4440,8 +4493,8 @@
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A120">
-        <v>46001</v>
+      <c r="A120" s="12">
+        <v>13701</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>38</v>
@@ -4460,8 +4513,8 @@
       </c>
     </row>
     <row r="121" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A121">
-        <v>46201</v>
+      <c r="A121" s="12">
+        <v>13703</v>
       </c>
       <c r="B121" s="8" t="s">
         <v>20</v>
@@ -4477,8 +4530,8 @@
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A122">
-        <v>46201</v>
+      <c r="A122" s="12">
+        <v>13703</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>38</v>
@@ -4497,8 +4550,8 @@
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A123">
-        <v>46201</v>
+      <c r="A123" s="12">
+        <v>13703</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>20</v>
@@ -4514,8 +4567,8 @@
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A124">
-        <v>46201</v>
+      <c r="A124" s="12">
+        <v>13703</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>38</v>
@@ -4534,8 +4587,8 @@
       </c>
     </row>
     <row r="125" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A125">
-        <v>46101</v>
+      <c r="A125" s="12">
+        <v>13702</v>
       </c>
       <c r="B125" s="8" t="s">
         <v>20</v>
@@ -4551,8 +4604,8 @@
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A126">
-        <v>46101</v>
+      <c r="A126" s="12">
+        <v>13702</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>38</v>
@@ -4571,8 +4624,8 @@
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A127">
-        <v>46101</v>
+      <c r="A127" s="12">
+        <v>13702</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>20</v>
@@ -4588,8 +4641,8 @@
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A128">
-        <v>46101</v>
+      <c r="A128" s="12">
+        <v>13702</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>38</v>
@@ -4608,8 +4661,8 @@
       </c>
     </row>
     <row r="129" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A129">
-        <v>46201</v>
+      <c r="A129" s="12">
+        <v>13703</v>
       </c>
       <c r="B129" s="8" t="s">
         <v>20</v>
@@ -4625,8 +4678,8 @@
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A130">
-        <v>46201</v>
+      <c r="A130" s="12">
+        <v>13703</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>38</v>
@@ -4645,8 +4698,8 @@
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A131">
-        <v>46201</v>
+      <c r="A131" s="12">
+        <v>13703</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>20</v>
@@ -4662,8 +4715,8 @@
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A132">
-        <v>46201</v>
+      <c r="A132" s="12">
+        <v>13703</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>38</v>
@@ -4682,8 +4735,8 @@
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A133">
-        <v>51301</v>
+      <c r="A133" s="12">
+        <v>14208</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>20</v>
@@ -4699,8 +4752,8 @@
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A134">
-        <v>51301</v>
+      <c r="A134" s="12">
+        <v>14208</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>18</v>
@@ -4719,8 +4772,8 @@
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A135">
-        <v>52106</v>
+      <c r="A135" s="12">
+        <v>14208</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>20</v>
@@ -4736,8 +4789,8 @@
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A136">
-        <v>52106</v>
+      <c r="A136" s="12">
+        <v>14208</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>18</v>
@@ -4756,8 +4809,8 @@
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A137">
-        <v>52701</v>
+      <c r="A137" s="12">
+        <v>14222</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>20</v>
@@ -4776,8 +4829,8 @@
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A138">
-        <v>52701</v>
+      <c r="A138" s="12">
+        <v>14222</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>18</v>
@@ -4796,8 +4849,8 @@
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A139">
-        <v>52701</v>
+      <c r="A139" s="12">
+        <v>14222</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>18</v>
@@ -4816,8 +4869,8 @@
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A140">
-        <v>52801</v>
+      <c r="A140" s="12">
+        <v>14223</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>20</v>
@@ -4833,8 +4886,8 @@
       </c>
     </row>
     <row r="141" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A141">
-        <v>52801</v>
+      <c r="A141" s="12">
+        <v>14223</v>
       </c>
       <c r="B141" s="9" t="s">
         <v>20</v>
@@ -4853,8 +4906,8 @@
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A142">
-        <v>52801</v>
+      <c r="A142" s="12">
+        <v>14223</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>38</v>
@@ -4873,8 +4926,8 @@
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A143">
-        <v>52801</v>
+      <c r="A143" s="12">
+        <v>14223</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>20</v>
@@ -4893,8 +4946,8 @@
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A144">
-        <v>52801</v>
+      <c r="A144" s="12">
+        <v>14223</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>38</v>
@@ -4913,8 +4966,8 @@
       </c>
     </row>
     <row r="145" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A145">
-        <v>52801</v>
+      <c r="A145" s="12">
+        <v>14223</v>
       </c>
       <c r="B145" s="9" t="s">
         <v>20</v>
@@ -4933,8 +4986,8 @@
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A146">
-        <v>52801</v>
+      <c r="A146" s="12">
+        <v>14223</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>38</v>
@@ -4953,8 +5006,8 @@
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A147">
-        <v>52801</v>
+      <c r="A147" s="12">
+        <v>14223</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>20</v>
@@ -4973,8 +5026,8 @@
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A148">
-        <v>52801</v>
+      <c r="A148" s="12">
+        <v>14223</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>38</v>
@@ -4993,8 +5046,8 @@
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A149">
-        <v>52801</v>
+      <c r="A149" s="12">
+        <v>14223</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>20</v>
@@ -5013,8 +5066,8 @@
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A150">
-        <v>52801</v>
+      <c r="A150" s="12">
+        <v>14223</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>18</v>
@@ -5033,8 +5086,8 @@
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A151" t="s">
-        <v>531</v>
+      <c r="A151" s="12" t="s">
+        <v>534</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>155</v>
@@ -5050,8 +5103,8 @@
       </c>
     </row>
     <row r="152" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A152">
-        <v>52701</v>
+      <c r="A152" s="12">
+        <v>14224</v>
       </c>
       <c r="B152" s="8" t="s">
         <v>20</v>
@@ -5067,8 +5120,8 @@
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A153">
-        <v>52702</v>
+      <c r="A153" s="12">
+        <v>14225</v>
       </c>
       <c r="B153" s="2" t="s">
         <v>20</v>
@@ -5087,8 +5140,8 @@
       </c>
     </row>
     <row r="154" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A154">
-        <v>52701</v>
+      <c r="A154" s="12">
+        <v>14224</v>
       </c>
       <c r="B154" s="8" t="s">
         <v>20</v>
@@ -5104,8 +5157,8 @@
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A155">
-        <v>52702</v>
+      <c r="A155" s="12">
+        <v>14225</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>20</v>
@@ -5124,8 +5177,8 @@
       </c>
     </row>
     <row r="156" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A156">
-        <v>52701</v>
+      <c r="A156" s="12">
+        <v>14224</v>
       </c>
       <c r="B156" s="8" t="s">
         <v>20</v>
@@ -5141,8 +5194,8 @@
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A157">
-        <v>52702</v>
+      <c r="A157" s="12">
+        <v>14225</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>20</v>
@@ -5161,8 +5214,8 @@
       </c>
     </row>
     <row r="158" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A158">
-        <v>52701</v>
+      <c r="A158" s="12">
+        <v>14224</v>
       </c>
       <c r="B158" s="8" t="s">
         <v>20</v>
@@ -5178,8 +5231,8 @@
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A159">
-        <v>52702</v>
+      <c r="A159" s="12">
+        <v>14225</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>20</v>
@@ -5198,8 +5251,8 @@
       </c>
     </row>
     <row r="160" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A160">
-        <v>52701</v>
+      <c r="A160" s="12">
+        <v>14224</v>
       </c>
       <c r="B160" s="8" t="s">
         <v>20</v>
@@ -5215,8 +5268,8 @@
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A161">
-        <v>52702</v>
+      <c r="A161" s="12">
+        <v>14225</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>20</v>
@@ -5235,8 +5288,8 @@
       </c>
     </row>
     <row r="162" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A162">
-        <v>52701</v>
+      <c r="A162" s="12">
+        <v>14224</v>
       </c>
       <c r="B162" s="8" t="s">
         <v>20</v>
@@ -5252,8 +5305,8 @@
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A163">
-        <v>52702</v>
+      <c r="A163" s="12">
+        <v>14225</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>20</v>
@@ -5272,8 +5325,8 @@
       </c>
     </row>
     <row r="164" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A164">
-        <v>52701</v>
+      <c r="A164" s="12">
+        <v>14224</v>
       </c>
       <c r="B164" s="8" t="s">
         <v>20</v>
@@ -5289,8 +5342,8 @@
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A165">
-        <v>52702</v>
+      <c r="A165" s="12">
+        <v>14225</v>
       </c>
       <c r="B165" s="2" t="s">
         <v>20</v>
@@ -5309,8 +5362,8 @@
       </c>
     </row>
     <row r="166" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A166">
-        <v>52701</v>
+      <c r="A166" s="12">
+        <v>14224</v>
       </c>
       <c r="B166" s="8" t="s">
         <v>20</v>
@@ -5326,8 +5379,8 @@
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A167">
-        <v>52702</v>
+      <c r="A167" s="12">
+        <v>14225</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>20</v>
@@ -5346,8 +5399,8 @@
       </c>
     </row>
     <row r="168" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A168">
-        <v>52701</v>
+      <c r="A168" s="12">
+        <v>14224</v>
       </c>
       <c r="B168" s="8" t="s">
         <v>20</v>
@@ -5363,8 +5416,8 @@
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A169">
-        <v>52702</v>
+      <c r="A169" s="12">
+        <v>14225</v>
       </c>
       <c r="B169" s="2" t="s">
         <v>20</v>
@@ -5383,8 +5436,8 @@
       </c>
     </row>
     <row r="170" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A170">
-        <v>52701</v>
+      <c r="A170" s="12">
+        <v>14224</v>
       </c>
       <c r="B170" s="8" t="s">
         <v>20</v>
@@ -5400,8 +5453,8 @@
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A171">
-        <v>52702</v>
+      <c r="A171" s="12">
+        <v>14225</v>
       </c>
       <c r="B171" s="2" t="s">
         <v>20</v>
@@ -5420,8 +5473,8 @@
       </c>
     </row>
     <row r="172" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A172">
-        <v>52701</v>
+      <c r="A172" s="12">
+        <v>14224</v>
       </c>
       <c r="B172" s="8" t="s">
         <v>20</v>
@@ -5437,8 +5490,8 @@
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A173">
-        <v>52702</v>
+      <c r="A173" s="12">
+        <v>14225</v>
       </c>
       <c r="B173" s="2" t="s">
         <v>20</v>
@@ -5457,8 +5510,8 @@
       </c>
     </row>
     <row r="174" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A174">
-        <v>52701</v>
+      <c r="A174" s="12">
+        <v>14226</v>
       </c>
       <c r="B174" s="8" t="s">
         <v>20</v>
@@ -5474,8 +5527,8 @@
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A175">
-        <v>52702</v>
+      <c r="A175" s="12">
+        <v>14227</v>
       </c>
       <c r="B175" s="2" t="s">
         <v>20</v>
@@ -5494,8 +5547,8 @@
       </c>
     </row>
     <row r="176" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A176">
-        <v>52701</v>
+      <c r="A176" s="12">
+        <v>14226</v>
       </c>
       <c r="B176" s="8" t="s">
         <v>20</v>
@@ -5511,8 +5564,8 @@
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A177">
-        <v>52702</v>
+      <c r="A177" s="12">
+        <v>14227</v>
       </c>
       <c r="B177" s="2" t="s">
         <v>20</v>
@@ -5531,8 +5584,8 @@
       </c>
     </row>
     <row r="178" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A178">
-        <v>53001</v>
+      <c r="A178" s="12">
+        <v>14226</v>
       </c>
       <c r="B178" s="8" t="s">
         <v>20</v>
@@ -5548,8 +5601,8 @@
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A179">
-        <v>53002</v>
+      <c r="A179" s="12">
+        <v>14227</v>
       </c>
       <c r="B179" s="2" t="s">
         <v>20</v>
@@ -5568,8 +5621,8 @@
       </c>
     </row>
     <row r="180" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A180">
-        <v>53001</v>
+      <c r="A180" s="12">
+        <v>14226</v>
       </c>
       <c r="B180" s="8" t="s">
         <v>20</v>
@@ -5585,8 +5638,8 @@
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A181">
-        <v>53002</v>
+      <c r="A181" s="12">
+        <v>14227</v>
       </c>
       <c r="B181" s="2" t="s">
         <v>20</v>
@@ -5605,8 +5658,8 @@
       </c>
     </row>
     <row r="182" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A182">
-        <v>53001</v>
+      <c r="A182" s="12">
+        <v>14226</v>
       </c>
       <c r="B182" s="8" t="s">
         <v>20</v>
@@ -5622,8 +5675,8 @@
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A183">
-        <v>53002</v>
+      <c r="A183" s="12">
+        <v>14227</v>
       </c>
       <c r="B183" s="2" t="s">
         <v>20</v>
@@ -5642,8 +5695,8 @@
       </c>
     </row>
     <row r="184" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A184">
-        <v>53001</v>
+      <c r="A184" s="12">
+        <v>14226</v>
       </c>
       <c r="B184" s="8" t="s">
         <v>20</v>
@@ -5659,8 +5712,8 @@
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A185">
-        <v>53002</v>
+      <c r="A185" s="12">
+        <v>14227</v>
       </c>
       <c r="B185" s="2" t="s">
         <v>20</v>
@@ -5679,8 +5732,8 @@
       </c>
     </row>
     <row r="186" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A186">
-        <v>53001</v>
+      <c r="A186" s="12">
+        <v>14226</v>
       </c>
       <c r="B186" s="8" t="s">
         <v>20</v>
@@ -5696,8 +5749,8 @@
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A187">
-        <v>53002</v>
+      <c r="A187" s="12">
+        <v>14227</v>
       </c>
       <c r="B187" s="2" t="s">
         <v>20</v>
@@ -5716,8 +5769,8 @@
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A188">
-        <v>53003</v>
+      <c r="A188" s="12">
+        <v>14228</v>
       </c>
       <c r="B188" s="2" t="s">
         <v>20</v>
@@ -5733,8 +5786,8 @@
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A189">
-        <v>53003</v>
+      <c r="A189" s="12">
+        <v>14228</v>
       </c>
       <c r="B189" s="2" t="s">
         <v>18</v>
@@ -5753,8 +5806,8 @@
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A190">
-        <v>53003</v>
+      <c r="A190" s="12">
+        <v>14228</v>
       </c>
       <c r="B190" s="2" t="s">
         <v>20</v>
@@ -5770,8 +5823,8 @@
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A191">
-        <v>53003</v>
+      <c r="A191" s="12">
+        <v>14228</v>
       </c>
       <c r="B191" s="2" t="s">
         <v>18</v>
@@ -5791,7 +5844,7 @@
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B192" s="2" t="s">
         <v>18</v>
@@ -5807,7 +5860,7 @@
       </c>
     </row>
     <row r="193" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A193" t="s">
+      <c r="A193" s="2" t="s">
         <v>532</v>
       </c>
       <c r="B193" s="2" t="s">
@@ -5824,8 +5877,8 @@
       </c>
     </row>
     <row r="194" spans="1:75" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A194">
-        <v>15103</v>
+      <c r="A194" s="12">
+        <v>10503</v>
       </c>
       <c r="B194" s="2" t="s">
         <v>38</v>
@@ -5913,8 +5966,8 @@
       <c r="BW194" s="2"/>
     </row>
     <row r="195" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A195">
-        <v>15103</v>
+      <c r="A195" s="12">
+        <v>10503</v>
       </c>
       <c r="B195" s="2" t="s">
         <v>38</v>
@@ -5933,8 +5986,8 @@
       </c>
     </row>
     <row r="196" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A196">
-        <v>15103</v>
+      <c r="A196" s="12">
+        <v>10503</v>
       </c>
       <c r="B196" s="2" t="s">
         <v>38</v>
@@ -5953,8 +6006,8 @@
       </c>
     </row>
     <row r="197" spans="1:75" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A197">
-        <v>15103</v>
+      <c r="A197" s="12">
+        <v>10503</v>
       </c>
       <c r="B197" s="2" t="s">
         <v>38</v>
@@ -6042,8 +6095,8 @@
       <c r="BW197" s="2"/>
     </row>
     <row r="198" spans="1:75" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A198">
-        <v>15103</v>
+      <c r="A198" s="12">
+        <v>10503</v>
       </c>
       <c r="B198" s="2" t="s">
         <v>18</v>
@@ -6129,8 +6182,8 @@
       <c r="BW198" s="2"/>
     </row>
     <row r="199" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A199">
-        <v>15103</v>
+      <c r="A199" s="12">
+        <v>10503</v>
       </c>
       <c r="B199" s="2" t="s">
         <v>38</v>
@@ -6149,8 +6202,8 @@
       </c>
     </row>
     <row r="200" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A200">
-        <v>15103</v>
+      <c r="A200" s="12">
+        <v>10503</v>
       </c>
       <c r="B200" s="2" t="s">
         <v>18</v>
@@ -6166,8 +6219,8 @@
       </c>
     </row>
     <row r="201" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A201">
-        <v>15103</v>
+      <c r="A201" s="12">
+        <v>10503</v>
       </c>
       <c r="B201" s="2" t="s">
         <v>38</v>
@@ -6186,8 +6239,8 @@
       </c>
     </row>
     <row r="202" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A202">
-        <v>15103</v>
+      <c r="A202" s="12">
+        <v>10503</v>
       </c>
       <c r="B202" s="2" t="s">
         <v>18</v>
@@ -6203,8 +6256,8 @@
       </c>
     </row>
     <row r="203" spans="1:75" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A203">
-        <v>15103</v>
+      <c r="A203" s="12">
+        <v>10503</v>
       </c>
       <c r="B203" s="2" t="s">
         <v>38</v>
@@ -6292,8 +6345,8 @@
       <c r="BW203" s="2"/>
     </row>
     <row r="204" spans="1:75" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A204">
-        <v>15103</v>
+      <c r="A204" s="12">
+        <v>10503</v>
       </c>
       <c r="B204" s="2" t="s">
         <v>18</v>
@@ -6379,8 +6432,8 @@
       <c r="BW204" s="2"/>
     </row>
     <row r="205" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A205">
-        <v>15103</v>
+      <c r="A205" s="12">
+        <v>10503</v>
       </c>
       <c r="B205" s="2" t="s">
         <v>38</v>
@@ -6399,8 +6452,8 @@
       </c>
     </row>
     <row r="206" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A206">
-        <v>15103</v>
+      <c r="A206" s="12">
+        <v>10503</v>
       </c>
       <c r="B206" s="2" t="s">
         <v>18</v>
@@ -6416,8 +6469,8 @@
       </c>
     </row>
     <row r="207" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A207">
-        <v>15103</v>
+      <c r="A207" s="12">
+        <v>10503</v>
       </c>
       <c r="B207" s="2" t="s">
         <v>38</v>
@@ -6436,8 +6489,8 @@
       </c>
     </row>
     <row r="208" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A208">
-        <v>15103</v>
+      <c r="A208" s="12">
+        <v>10503</v>
       </c>
       <c r="B208" s="2" t="s">
         <v>18</v>
@@ -6453,8 +6506,8 @@
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A209">
-        <v>16005</v>
+      <c r="A209" s="12">
+        <v>10609</v>
       </c>
       <c r="B209" s="2" t="s">
         <v>38</v>
@@ -6473,8 +6526,8 @@
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A210">
-        <v>16005</v>
+      <c r="A210" s="12">
+        <v>10609</v>
       </c>
       <c r="B210" s="2" t="s">
         <v>38</v>
@@ -6493,8 +6546,8 @@
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A211">
-        <v>16005</v>
+      <c r="A211" s="12">
+        <v>10609</v>
       </c>
       <c r="B211" s="2" t="s">
         <v>38</v>
@@ -6513,8 +6566,8 @@
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A212">
-        <v>16005</v>
+      <c r="A212" s="12">
+        <v>10609</v>
       </c>
       <c r="B212" s="2" t="s">
         <v>38</v>
@@ -6533,8 +6586,8 @@
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A213">
-        <v>16005</v>
+      <c r="A213" s="12">
+        <v>10609</v>
       </c>
       <c r="B213" s="2" t="s">
         <v>18</v>
@@ -6550,8 +6603,8 @@
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A214">
-        <v>16005</v>
+      <c r="A214" s="12">
+        <v>10609</v>
       </c>
       <c r="B214" s="2" t="s">
         <v>38</v>
@@ -6570,8 +6623,8 @@
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A215">
-        <v>16005</v>
+      <c r="A215" s="12">
+        <v>10609</v>
       </c>
       <c r="B215" s="2" t="s">
         <v>18</v>
@@ -6587,8 +6640,8 @@
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A216">
-        <v>16005</v>
+      <c r="A216" s="12">
+        <v>10609</v>
       </c>
       <c r="B216" s="2" t="s">
         <v>38</v>
@@ -6607,8 +6660,8 @@
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A217">
-        <v>16005</v>
+      <c r="A217" s="12">
+        <v>10609</v>
       </c>
       <c r="B217" s="2" t="s">
         <v>18</v>
@@ -6624,8 +6677,8 @@
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A218">
-        <v>16005</v>
+      <c r="A218" s="12">
+        <v>10609</v>
       </c>
       <c r="B218" s="2" t="s">
         <v>38</v>
@@ -6644,8 +6697,8 @@
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A219">
-        <v>16005</v>
+      <c r="A219" s="12">
+        <v>10609</v>
       </c>
       <c r="B219" s="2" t="s">
         <v>18</v>
@@ -6661,8 +6714,8 @@
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A220">
-        <v>16005</v>
+      <c r="A220" s="12">
+        <v>10609</v>
       </c>
       <c r="B220" s="2" t="s">
         <v>38</v>
@@ -6681,8 +6734,8 @@
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A221">
-        <v>16005</v>
+      <c r="A221" s="12">
+        <v>10609</v>
       </c>
       <c r="B221" s="2" t="s">
         <v>18</v>
@@ -6698,8 +6751,8 @@
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A222">
-        <v>16005</v>
+      <c r="A222" s="12">
+        <v>10609</v>
       </c>
       <c r="B222" s="2" t="s">
         <v>38</v>
@@ -6718,8 +6771,8 @@
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A223">
-        <v>16005</v>
+      <c r="A223" s="12">
+        <v>10609</v>
       </c>
       <c r="B223" s="2" t="s">
         <v>18</v>
@@ -6735,8 +6788,8 @@
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A224">
-        <v>16005</v>
+      <c r="A224" s="12">
+        <v>10610</v>
       </c>
       <c r="B224" s="2" t="s">
         <v>20</v>
@@ -6752,8 +6805,8 @@
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A225">
-        <v>16005</v>
+      <c r="A225" s="12">
+        <v>10610</v>
       </c>
       <c r="B225" s="2" t="s">
         <v>18</v>
@@ -6772,8 +6825,8 @@
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A226">
-        <v>16005</v>
+      <c r="A226" s="12" t="s">
+        <v>535</v>
       </c>
       <c r="B226" s="2" t="s">
         <v>18</v>
@@ -6824,7 +6877,7 @@
         <v>447</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
@@ -6845,10 +6898,10 @@
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="C8:C9">
-    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C34:C57">
-    <cfRule type="duplicateValues" dxfId="4" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="8"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6856,7 +6909,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D63B81B-C0DE-4D5C-B8D8-1821B93262B2}">
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.28515625" style="2" customWidth="1"/>
@@ -7111,95 +7164,95 @@
         <v>10000</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>513</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>514</v>
+        <v>536</v>
+      </c>
+      <c r="C16" s="10">
+        <v>1</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>515</v>
+        <v>537</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10">
         <v>10000</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>513</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>517</v>
+        <v>536</v>
+      </c>
+      <c r="C17" s="10">
+        <v>2</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>515</v>
+        <v>539</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10">
         <v>10000</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>513</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>518</v>
+        <v>536</v>
+      </c>
+      <c r="C18" s="10">
+        <v>3</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>515</v>
+        <v>541</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10">
         <v>10000</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>519</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>520</v>
+        <v>536</v>
+      </c>
+      <c r="C19" s="10">
+        <v>4</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>515</v>
+        <v>543</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10">
         <v>10000</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>519</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>521</v>
+        <v>536</v>
+      </c>
+      <c r="C20" s="10">
+        <v>5</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>515</v>
+        <v>545</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10">
         <v>10000</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="D21" s="10" t="s">
         <v>515</v>
@@ -7208,15 +7261,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="22" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10">
         <v>10000</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>523</v>
+        <v>513</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="D22" s="10" t="s">
         <v>515</v>
@@ -7225,15 +7278,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="23" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10">
         <v>10000</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>523</v>
+        <v>513</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="D23" s="10" t="s">
         <v>515</v>
@@ -7242,15 +7295,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="24" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10">
         <v>10000</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="D24" s="10" t="s">
         <v>515</v>
@@ -7259,15 +7312,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="25" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10">
         <v>10000</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="D25" s="10" t="s">
         <v>515</v>
@@ -7276,15 +7329,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="26" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10">
         <v>10000</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="D26" s="10" t="s">
         <v>515</v>
@@ -7293,15 +7346,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="27" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="10">
         <v>10000</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="D27" s="10" t="s">
         <v>515</v>
@@ -7310,202 +7363,290 @@
         <v>516</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>51001</v>
-      </c>
-      <c r="B28" s="3" t="s">
+    <row r="28" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="10">
+        <v>10000</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>523</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>525</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>515</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="10">
+        <v>10000</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>523</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>526</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>515</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="10">
+        <v>10000</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>527</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>528</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>515</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="10">
+        <v>10000</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>527</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>529</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>515</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="10">
+        <v>10000</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>527</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>530</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>515</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="12">
+        <v>14201</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C33" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D33" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>51001</v>
-      </c>
-      <c r="B29" s="3" t="s">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="12">
+        <v>14201</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C34" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D34" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>51001</v>
-      </c>
-      <c r="B30" s="3" t="s">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="12">
+        <v>14201</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C35" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D35" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="J30" s="2" t="s">
+      <c r="J35" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>51001</v>
-      </c>
-      <c r="B31" s="3" t="s">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="12">
+        <v>14201</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C36" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D36" s="2" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>51001</v>
-      </c>
-      <c r="B32" s="3" t="s">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="12">
+        <v>14201</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C37" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D37" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>51001</v>
-      </c>
-      <c r="B33" s="2" t="s">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="12">
+        <v>14201</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C38" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D38" s="2" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>51001</v>
-      </c>
-      <c r="B34" s="2" t="s">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="12">
+        <v>14201</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C39" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D39" s="2" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>51001</v>
-      </c>
-      <c r="B35" s="2" t="s">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="12">
+        <v>14201</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C40" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D40" s="2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>51001</v>
-      </c>
-      <c r="B36" s="2" t="s">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="12">
+        <v>14201</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C41" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="D41" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>52105</v>
-      </c>
-      <c r="B37" s="2" t="s">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="12">
+        <v>14405</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C42" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="D42" s="2" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>52105</v>
-      </c>
-      <c r="B38" s="2" t="s">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="12">
+        <v>14405</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C43" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="D43" s="2" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>52105</v>
-      </c>
-      <c r="B39" s="2" t="s">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="12">
+        <v>14405</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C44" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D44" s="2" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>52105</v>
-      </c>
-      <c r="B40" s="2" t="s">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="12">
+        <v>14405</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C45" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="D45" s="2" t="s">
         <v>118</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C4:C6">
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C7:C10">
     <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C7:C10">
+  <conditionalFormatting sqref="C11:C12">
     <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C11:C12">
+  <conditionalFormatting sqref="C21:C32">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:C27">
+  <conditionalFormatting sqref="C16:C20">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7548,26 +7689,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="d0fa6634-326e-4532-91a2-52bea7ac9212" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4877444-78fa-4cfa-bafc-d6c64fafc061">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DE51FB2AFBB2DD429D3D11FE759FFC43" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1354c8e90e28409d311bbba5db8dc335">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f4877444-78fa-4cfa-bafc-d6c64fafc061" xmlns:ns3="d0fa6634-326e-4532-91a2-52bea7ac9212" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dbb4473bd7833dc3543803a005841490" ns2:_="" ns3:_="">
     <xsd:import namespace="f4877444-78fa-4cfa-bafc-d6c64fafc061"/>
@@ -7808,26 +7929,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08E67F88-34D7-4F06-AD9D-1E85A09096B5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d0fa6634-326e-4532-91a2-52bea7ac9212"/>
-    <ds:schemaRef ds:uri="f4877444-78fa-4cfa-bafc-d6c64fafc061"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="d0fa6634-326e-4532-91a2-52bea7ac9212" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4877444-78fa-4cfa-bafc-d6c64fafc061">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38DBD55A-6A6F-4CFC-88B1-45940F719B9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EEE20FAB-4766-46A5-8028-431F2E6E2BC1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7844,4 +7966,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08E67F88-34D7-4F06-AD9D-1E85A09096B5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d0fa6634-326e-4532-91a2-52bea7ac9212"/>
+    <ds:schemaRef ds:uri="f4877444-78fa-4cfa-bafc-d6c64fafc061"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38DBD55A-6A6F-4CFC-88B1-45940F719B9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>